--- a/tracking_forms/007_freight_route_optimization_report_form--tracking_forms.xlsx
+++ b/tracking_forms/007_freight_route_optimization_report_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,8 +1171,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'highway'}</t>
+          <t>highway</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Highway'}</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'railway'}</t>
+          <t>railway</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Railway'}</t>
+          <t>Railway</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'waterway'}</t>
+          <t>waterway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Waterway'}</t>
+          <t>Waterway</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'logistics'}</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Logistics'}</t>
+          <t>Logistics</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'traffic_jam'}</t>
+          <t>traffic_jam</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Traffic Jam'}</t>
+          <t>Traffic Jam</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'weather_conditions'}</t>
+          <t>weather_conditions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Weather Conditions'}</t>
+          <t>Weather Conditions</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'road_conditions'}</t>
+          <t>road_conditions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Road Conditions'}</t>
+          <t>Road Conditions</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'trucking'}</t>
+          <t>trucking</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Trucking'}</t>
+          <t>Trucking</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'rail'}</t>
+          <t>rail</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Rail'}</t>
+          <t>Rail</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'ship'}</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Ship'}</t>
+          <t>Ship</t>
         </is>
       </c>
     </row>
